--- a/docentes/Flores Ovalle Victor - Estadisticos 20222.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="122">
   <si>
     <t>Mat</t>
   </si>
@@ -73,9 +73,84 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>GAYTAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LLAME</t>
+  </si>
+  <si>
     <t>MARIANO</t>
   </si>
   <si>
+    <t>MARES</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>ESPERON</t>
   </si>
   <si>
@@ -109,13 +184,61 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>ANTONIO</t>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>APOLINAR</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
   </si>
   <si>
     <t>MORA</t>
@@ -139,19 +262,85 @@
     <t>MEJIA</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>ZACARIAS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>FERNANDA</t>
+  </si>
+  <si>
+    <t>ANA SHECIT</t>
+  </si>
+  <si>
+    <t>JOSAVIA ARIDAI</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>MARIA ANGELES</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ARACELI</t>
+  </si>
+  <si>
+    <t>BRENDA</t>
   </si>
   <si>
     <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>JULIO ANTONIO</t>
+  </si>
+  <si>
+    <t>JOSE ALBIN</t>
+  </si>
+  <si>
+    <t>ATZIN LUCERO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>NATHALI</t>
+  </si>
+  <si>
+    <t>KAREN ARLET</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>EMILY</t>
   </si>
   <si>
     <t>MIA VALENTINA</t>
@@ -806,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -838,16 +1027,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920237</v>
+        <v>22330051920231</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -861,22 +1050,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920197</v>
+        <v>22330051920260</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -884,22 +1073,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920198</v>
+        <v>22330051920234</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -907,22 +1096,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920199</v>
+        <v>22330051920238</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -930,22 +1119,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920201</v>
+        <v>22330051920241</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -953,22 +1142,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920280</v>
+        <v>22330051920243</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -976,22 +1165,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920204</v>
+        <v>22330051920245</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -999,22 +1188,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920206</v>
+        <v>22330051920318</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1022,22 +1211,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920290</v>
+        <v>22330051920319</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1045,22 +1234,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920209</v>
+        <v>20330051920237</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1068,22 +1257,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920210</v>
+        <v>22330051920414</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1091,22 +1280,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920212</v>
+        <v>22330051920248</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1114,22 +1303,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920213</v>
+        <v>22330051920250</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1137,22 +1326,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920215</v>
+        <v>22330051920399</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1160,25 +1349,600 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
+        <v>22330051920235</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920254</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920257</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920256</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920190</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920192</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920196</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920200</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920202</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920217</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920218</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920219</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920197</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920198</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920199</v>
+      </c>
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920201</v>
+      </c>
+      <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>19330051920280</v>
+      </c>
+      <c r="B32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920204</v>
+      </c>
+      <c r="B33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920206</v>
+      </c>
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>19330051920290</v>
+      </c>
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" t="s">
+        <v>115</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>20330051920209</v>
+      </c>
+      <c r="B36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>20330051920210</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920212</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>20330051920213</v>
+      </c>
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>20330051920215</v>
+      </c>
+      <c r="B40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
         <v>20330051920259</v>
       </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
+      <c r="B41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20222.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20222.xlsx
@@ -516,7 +516,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>74.42</v>
+        <v>73.81</v>
       </c>
       <c r="H2">
         <v>6.7</v>
@@ -607,13 +607,13 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -692,7 +692,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -701,10 +701,10 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>74.42</v>
+        <v>73.81</v>
       </c>
       <c r="H2">
         <v>6.7</v>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20222.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -79,9 +79,6 @@
     <t>ASCENCION</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
     <t>GAYTAN</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -107,9 +101,6 @@
   </si>
   <si>
     <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
@@ -743,7 +734,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -781,10 +772,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -804,10 +795,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -821,45 +812,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920196</v>
+        <v>22330051920241</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920241</v>
+        <v>20330051920210</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -867,16 +858,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920210</v>
+        <v>20330051920259</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -885,29 +876,6 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920259</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20222.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -76,40 +76,28 @@
     <t>MARIANO</t>
   </si>
   <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
     <t>ASCENCION</t>
   </si>
   <si>
-    <t>GAYTAN</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>JACQUELINE</t>
   </si>
   <si>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
     <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
   </si>
 </sst>
 </file>
@@ -601,16 +589,19 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>69.05</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -624,16 +615,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.62</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -689,16 +683,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>73.81</v>
+        <v>69.05</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -715,16 +709,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>76.92</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +728,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -772,10 +766,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -789,22 +783,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920190</v>
+        <v>22330051920400</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -812,71 +806,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920241</v>
+        <v>20330051920190</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920210</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920259</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20222.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -76,28 +76,10 @@
     <t>MARIANO</t>
   </si>
   <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
   </si>
 </sst>
 </file>
@@ -683,16 +665,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>69.05</v>
+        <v>92.86</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -709,16 +691,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -728,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -766,10 +748,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -778,52 +760,6 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920400</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920190</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>
